--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N45_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N45_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>68.1464233389918</v>
+        <v>11.07379379258617</v>
       </c>
       <c r="D2" t="n">
-        <v>66.30076787024868</v>
+        <v>10.77387477891541</v>
       </c>
       <c r="E2" t="n">
-        <v>18.49064803633594</v>
+        <v>3.00473030590459</v>
       </c>
       <c r="F2" t="n">
-        <v>17.7186864014049</v>
+        <v>2.879286540228296</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>66.80457801934294</v>
+        <v>10.85574392814323</v>
       </c>
       <c r="D3" t="n">
-        <v>65.48429799463263</v>
+        <v>10.6411984241278</v>
       </c>
       <c r="E3" t="n">
-        <v>18.49064803633594</v>
+        <v>3.00473030590459</v>
       </c>
       <c r="F3" t="n">
-        <v>17.7186864014049</v>
+        <v>2.879286540228296</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>32.42854876362369</v>
+        <v>5.26963917408885</v>
       </c>
       <c r="D4" t="n">
-        <v>30.91073428387519</v>
+        <v>5.022994321129719</v>
       </c>
       <c r="E4" t="n">
-        <v>18.49064803633594</v>
+        <v>3.00473030590459</v>
       </c>
       <c r="F4" t="n">
-        <v>17.7186864014049</v>
+        <v>2.879286540228296</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>39.39999700292872</v>
+        <v>6.402499512975917</v>
       </c>
       <c r="D5" t="n">
-        <v>60.43555633370151</v>
+        <v>9.820777904226496</v>
       </c>
       <c r="E5" t="n">
-        <v>18.49064803633594</v>
+        <v>3.00473030590459</v>
       </c>
       <c r="F5" t="n">
-        <v>17.7186864014049</v>
+        <v>2.879286540228296</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>42.86315434029558</v>
+        <v>6.965262580298032</v>
       </c>
       <c r="D6" t="n">
-        <v>60.25642424199073</v>
+        <v>9.791668939323493</v>
       </c>
       <c r="E6" t="n">
-        <v>18.49064803633594</v>
+        <v>3.00473030590459</v>
       </c>
       <c r="F6" t="n">
-        <v>17.7186864014049</v>
+        <v>2.879286540228296</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>26.70674072214728</v>
+        <v>4.339845367348934</v>
       </c>
       <c r="D7" t="n">
-        <v>50.74268925304105</v>
+        <v>8.245687003619171</v>
       </c>
       <c r="E7" t="n">
-        <v>18.49064803633594</v>
+        <v>3.00473030590459</v>
       </c>
       <c r="F7" t="n">
-        <v>17.7186864014049</v>
+        <v>2.879286540228296</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>12.75417200817182</v>
+        <v>2.072552951327921</v>
       </c>
       <c r="D8" t="n">
-        <v>10.26743094259756</v>
+        <v>1.668457528172104</v>
       </c>
       <c r="E8" t="n">
-        <v>18.49064803633594</v>
+        <v>3.00473030590459</v>
       </c>
       <c r="F8" t="n">
-        <v>17.7186864014049</v>
+        <v>2.879286540228296</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>63.59496123966823</v>
+        <v>10.33418120144609</v>
       </c>
       <c r="D9" t="n">
-        <v>51.53882032022076</v>
+        <v>8.375058302035873</v>
       </c>
       <c r="E9" t="n">
-        <v>18.49064803633594</v>
+        <v>3.00473030590459</v>
       </c>
       <c r="F9" t="n">
-        <v>17.7186864014049</v>
+        <v>2.879286540228296</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>58.76231379263761</v>
+        <v>9.548875991303611</v>
       </c>
       <c r="D10" t="n">
-        <v>42.573465914816</v>
+        <v>6.918188211157601</v>
       </c>
       <c r="E10" t="n">
-        <v>18.49064803633594</v>
+        <v>3.00473030590459</v>
       </c>
       <c r="F10" t="n">
-        <v>17.7186864014049</v>
+        <v>2.879286540228296</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>62.87602445422889</v>
+        <v>10.21735397381219</v>
       </c>
       <c r="D11" t="n">
-        <v>56.37597005817283</v>
+        <v>9.161095134453086</v>
       </c>
       <c r="E11" t="n">
-        <v>18.49064803633594</v>
+        <v>3.00473030590459</v>
       </c>
       <c r="F11" t="n">
-        <v>17.7186864014049</v>
+        <v>2.879286540228296</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>23.22384795255053</v>
+        <v>3.773875292289461</v>
       </c>
       <c r="D12" t="n">
-        <v>17.44132902023291</v>
+        <v>2.834215965787848</v>
       </c>
       <c r="E12" t="n">
-        <v>18.49064803633594</v>
+        <v>3.00473030590459</v>
       </c>
       <c r="F12" t="n">
-        <v>17.7186864014049</v>
+        <v>2.879286540228296</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>59.81487187158044</v>
+        <v>9.719916679131822</v>
       </c>
       <c r="D13" t="n">
-        <v>37.52998800959041</v>
+        <v>6.098623051558442</v>
       </c>
       <c r="E13" t="n">
-        <v>18.49064803633594</v>
+        <v>3.00473030590459</v>
       </c>
       <c r="F13" t="n">
-        <v>17.7186864014049</v>
+        <v>2.879286540228296</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
